--- a/documents/reports/gaia_parameter_matrix.xlsx
+++ b/documents/reports/gaia_parameter_matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/waltzerclone/WALTzER-simulator/output/20260312_213012_769608/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/waltzerclone/WALTzER-simulator/documents/reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E6AB1B-F309-FD42-890D-9932ED11B182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EC859F-2464-A946-B419-10A458E30863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11600" yWindow="3000" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15300" yWindow="3480" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gaia_parameters" sheetId="1" r:id="rId1"/>
@@ -1795,33 +1795,15 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="GaiaParameters" displayName="GaiaParameters" ref="A1:I554">
-  <autoFilter ref="A1:I554" xr:uid="{00000000-0009-0000-0100-000001000000}">
+  <autoFilter ref="A1:I554" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="mh_gspphot"/>
-        <filter val="mh_gspphot_a"/>
-        <filter val="mh_gspphot_a_lower"/>
-        <filter val="mh_gspphot_a_upper"/>
-        <filter val="mh_gspphot_lower"/>
-        <filter val="mh_gspphot_marcs"/>
-        <filter val="mh_gspphot_marcs_lower"/>
-        <filter val="mh_gspphot_marcs_upper"/>
-        <filter val="mh_gspphot_ob"/>
-        <filter val="mh_gspphot_ob_lower"/>
-        <filter val="mh_gspphot_ob_upper"/>
-        <filter val="mh_gspphot_phoenix"/>
-        <filter val="mh_gspphot_phoenix_lower"/>
-        <filter val="mh_gspphot_phoenix_upper"/>
-        <filter val="mh_gspphot_upper"/>
-        <filter val="mh_gspspec"/>
-        <filter val="mh_gspspec_ann"/>
-        <filter val="mh_gspspec_ann_lower"/>
-        <filter val="mh_gspspec_ann_upper"/>
-        <filter val="mh_gspspec_lower"/>
-        <filter val="mh_gspspec_upper"/>
-        <filter val="mh_msc"/>
-        <filter val="mh_msc_lower"/>
-        <filter val="mh_msc_upper"/>
+        <filter val="grvs_mag"/>
+        <filter val="grvs_mag_error"/>
+        <filter val="grvs_mag_nb_transits"/>
+        <filter val="phot_bp_mean_mag"/>
+        <filter val="phot_g_mean_mag"/>
+        <filter val="phot_rp_mean_mag"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4909,7 +4891,7 @@
         <v>0.37000000476837158</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -4923,7 +4905,7 @@
         <v>-1.4907000064849849</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>9</v>
       </c>
@@ -4937,7 +4919,7 @@
         <v>-1.4977999925613401</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -4951,7 +4933,7 @@
         <v>-1.473099946975708</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>9</v>
       </c>
@@ -4974,7 +4956,7 @@
         <v>-0.41999998688697809</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>9</v>
       </c>
@@ -4997,7 +4979,7 @@
         <v>-0.43999999761581421</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>9</v>
       </c>
@@ -5020,7 +5002,7 @@
         <v>-0.40000000596046448</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>9</v>
       </c>
@@ -5049,7 +5031,7 @@
         <v>0.43660473823547358</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>9</v>
       </c>
@@ -5078,7 +5060,7 @@
         <v>0.36187809705734247</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -7740,7 +7722,7 @@
         <v>1.6255999803543091</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>252</v>
       </c>
@@ -7754,7 +7736,7 @@
         <v>-1.4907000064849849</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>252</v>
       </c>
@@ -7768,7 +7750,7 @@
         <v>-1.4977999925613401</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>252</v>
       </c>
@@ -7782,7 +7764,7 @@
         <v>-1.473099946975708</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>252</v>
       </c>
@@ -7793,7 +7775,7 @@
         <v>-0.28130000829696661</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>252</v>
       </c>
@@ -7804,7 +7786,7 @@
         <v>-0.37490001320838928</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>252</v>
       </c>
@@ -7815,7 +7797,7 @@
         <v>-0.22640000283718109</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>252</v>
       </c>
@@ -7823,7 +7805,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>252</v>
       </c>
@@ -7831,7 +7813,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>252</v>
       </c>
@@ -7839,7 +7821,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>252</v>
       </c>
@@ -7853,7 +7835,7 @@
         <v>-0.99409997463226318</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>252</v>
       </c>
@@ -7867,7 +7849,7 @@
         <v>-0.99919998645782471</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>252</v>
       </c>
@@ -7881,7 +7863,7 @@
         <v>-0.96979999542236328</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>252</v>
       </c>
@@ -7904,7 +7886,7 @@
         <v>-0.17000000178813929</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>252</v>
       </c>
@@ -7927,7 +7909,7 @@
         <v>-0.2199999988079071</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>252</v>
       </c>
@@ -9413,7 +9395,7 @@
         <v>1.1398839950561519</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>430</v>
       </c>
@@ -9439,7 +9421,7 @@
         <v>9.031346321105957</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>430</v>
       </c>
@@ -9465,7 +9447,7 @@
         <v>6.0382578521966934E-3</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>430</v>
       </c>
@@ -10040,7 +10022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>430</v>
       </c>
@@ -10054,7 +10036,7 @@
         <v>-1.4907000064849849</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>430</v>
       </c>
@@ -10068,7 +10050,7 @@
         <v>-1.4977999925613401</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>430</v>
       </c>
@@ -10409,7 +10391,7 @@
         <v>327.44546508789062</v>
       </c>
     </row>
-    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>430</v>
       </c>
@@ -10641,7 +10623,7 @@
         <v>1480.75634765625</v>
       </c>
     </row>
-    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>430</v>
       </c>
@@ -10815,7 +10797,7 @@
         <v>682.83917236328125</v>
       </c>
     </row>
-    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>430</v>
       </c>

--- a/documents/reports/gaia_parameter_matrix.xlsx
+++ b/documents/reports/gaia_parameter_matrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/waltzerclone/WALTzER-simulator/documents/reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreatanzer/Documents/Space Science/MasterThesis/WALTzER-simulator/documents/reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EC859F-2464-A946-B419-10A458E30863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60A5A85-AE26-AC47-9D7C-0CF37C9F9E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15300" yWindow="3480" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4580" yWindow="4800" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gaia_parameters" sheetId="1" r:id="rId1"/>
@@ -1798,12 +1798,27 @@
   <autoFilter ref="A1:I554" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="grvs_mag"/>
-        <filter val="grvs_mag_error"/>
-        <filter val="grvs_mag_nb_transits"/>
-        <filter val="phot_bp_mean_mag"/>
-        <filter val="phot_g_mean_mag"/>
-        <filter val="phot_rp_mean_mag"/>
+        <filter val="radius_flame"/>
+        <filter val="radius_flame_lower"/>
+        <filter val="radius_flame_spec"/>
+        <filter val="radius_flame_spec_lower"/>
+        <filter val="radius_flame_spec_upper"/>
+        <filter val="radius_flame_upper"/>
+        <filter val="radius_gspphot"/>
+        <filter val="radius_gspphot_a"/>
+        <filter val="radius_gspphot_a_lower"/>
+        <filter val="radius_gspphot_a_upper"/>
+        <filter val="radius_gspphot_lower"/>
+        <filter val="radius_gspphot_marcs"/>
+        <filter val="radius_gspphot_marcs_lower"/>
+        <filter val="radius_gspphot_marcs_upper"/>
+        <filter val="radius_gspphot_ob"/>
+        <filter val="radius_gspphot_ob_lower"/>
+        <filter val="radius_gspphot_ob_upper"/>
+        <filter val="radius_gspphot_phoenix"/>
+        <filter val="radius_gspphot_phoenix_lower"/>
+        <filter val="radius_gspphot_phoenix_upper"/>
+        <filter val="radius_gspphot_upper"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2110,6 +2125,7 @@
   <dimension ref="A1:I554"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="31.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5308,7 +5324,7 @@
         <v>-2.999999932944775E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>9</v>
       </c>
@@ -5322,7 +5338,7 @@
         <v>1.653521656990051</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -5336,7 +5352,7 @@
         <v>1.6200762987136841</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>9</v>
       </c>
@@ -5350,7 +5366,7 @@
         <v>1.686945915222168</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>9</v>
       </c>
@@ -5364,7 +5380,7 @@
         <v>1.659000039100647</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>9</v>
       </c>
@@ -5378,7 +5394,7 @@
         <v>1.653900027275085</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>9</v>
       </c>
@@ -7932,7 +7948,7 @@
         <v>-5.9999998658895493E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>252</v>
       </c>
@@ -7955,7 +7971,7 @@
         <v>85.533065795898438</v>
       </c>
     </row>
-    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>252</v>
       </c>
@@ -7978,7 +7994,7 @@
         <v>80.472206115722656</v>
       </c>
     </row>
-    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>252</v>
       </c>
@@ -8001,7 +8017,7 @@
         <v>94.854110717773438</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>252</v>
       </c>
@@ -8015,7 +8031,7 @@
         <v>1.659000039100647</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>252</v>
       </c>
@@ -8029,7 +8045,7 @@
         <v>1.653900027275085</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>252</v>
       </c>
@@ -8043,7 +8059,7 @@
         <v>1.6640000343322749</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>252</v>
       </c>
@@ -8054,7 +8070,7 @@
         <v>1.7726999521255491</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>252</v>
       </c>
@@ -8065,7 +8081,7 @@
         <v>1.699200034141541</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>252</v>
       </c>
@@ -8076,7 +8092,7 @@
         <v>1.995499968528748</v>
       </c>
     </row>
-    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>252</v>
       </c>
@@ -8084,7 +8100,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>252</v>
       </c>
@@ -8092,7 +8108,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>252</v>
       </c>
@@ -8100,7 +8116,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>252</v>
       </c>
@@ -8114,7 +8130,7 @@
         <v>1.6009000539779661</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>252</v>
       </c>
@@ -8128,7 +8144,7 @@
         <v>1.594200015068054</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>252</v>
       </c>
@@ -9395,7 +9411,7 @@
         <v>1.1398839950561519</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>430</v>
       </c>
@@ -9421,7 +9437,7 @@
         <v>9.031346321105957</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>430</v>
       </c>
@@ -9447,7 +9463,7 @@
         <v>6.0382578521966934E-3</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>430</v>
       </c>
@@ -10391,7 +10407,7 @@
         <v>327.44546508789062</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>430</v>
       </c>
@@ -10623,7 +10639,7 @@
         <v>1480.75634765625</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>430</v>
       </c>
@@ -10797,7 +10813,7 @@
         <v>682.83917236328125</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>430</v>
       </c>
